--- a/tests/testdata/excel/フォルダ/拡張子付きフォルダ.xlsx/中身.xlsx
+++ b/tests/testdata/excel/フォルダ/拡張子付きフォルダ.xlsx/中身.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3780766A-0B82-4DC9-958D-1146C42BCB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0CBAACB-72F0-4AAF-A73E-CA0D78C64354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{FA7E168E-0D8C-4F40-A36C-E009570C894D}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{670ECB35-69F4-4079-9B6D-3A9A61352D02}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74B2786-A887-482E-9F6A-4D224571BF77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27495D8D-1EF1-49E2-99C2-84861816D790}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/フォルダ/拡張子付きフォルダ.xlsx/中身.xlsx
+++ b/tests/testdata/excel/フォルダ/拡張子付きフォルダ.xlsx/中身.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0CBAACB-72F0-4AAF-A73E-CA0D78C64354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{78843A5D-081B-4CFA-8D01-372372AFFAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{670ECB35-69F4-4079-9B6D-3A9A61352D02}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{C23D164C-A263-4020-AE48-5C498071AE99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27495D8D-1EF1-49E2-99C2-84861816D790}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157FCFB3-4112-4DAB-8DA1-37FFBD5411F2}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
